--- a/AAII_Financials/Quarterly/PGR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PGR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="92">
   <si>
     <t>PGR</t>
   </si>
@@ -656,539 +656,551 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="10" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="11" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>23599000</v>
+      </c>
+      <c r="E8" s="3">
         <v>22180000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>22738000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>22502000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>21995000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>20402000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>20267000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>19712000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>18127000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>17237000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>16884500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>15553400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>15347400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>14297700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>13462900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>12774400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>11513300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>11835800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>12485100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>11852600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>11899200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>11439600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>11410300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>10942500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>10967200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>9318100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>10734800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>9524600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>9444500</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>9293800</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>8028800</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>8490000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>8011800</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>7424100</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>7115100</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>6786000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>6599100</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>6315900</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>6122100</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>5930200</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>19148000</v>
+      </c>
+      <c r="E9" s="3">
         <v>18413000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>18585000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>18015000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>17805000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>16979000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>17117000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>16570000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>16083000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>14135000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>14227100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>13981800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>14755400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>13597700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1049100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>970900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>933600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>963400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>958100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>951500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>928800</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>874400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>859700</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>835200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>795500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>782800</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>822500</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>751500</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>738600</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>710600</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>684000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>662700</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>630800</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>596200</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>567700</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>540100</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>514200</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>502900</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>489200</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>475400</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>4451000</v>
+      </c>
+      <c r="E10" s="3">
         <v>3767000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>4153000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>4487000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>4190000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>3423000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>3150000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>3142000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2044000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>3102000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2657400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1571600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>592000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>700000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>12413800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>11803500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>10579700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>10872400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>11527000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>10901100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>10970400</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>10565200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>10550600</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>10107300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>10171700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>8535300</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>9912300</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>8773100</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>8705900</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>8583200</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>7344800</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>7827300</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>7381000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>6827900</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>6547400</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>6245900</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>6084900</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>5813000</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>5632900</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>5454800</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1231,8 +1243,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1353,8 +1366,11 @@
       <c r="AP12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1475,8 +1491,11 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1519,18 +1538,18 @@
       <c r="P14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>224800</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1546,8 +1565,8 @@
       <c r="Y14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
+      <c r="Z14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA14" s="3">
         <v>0</v>
@@ -1561,14 +1580,14 @@
       <c r="AD14" s="3">
         <v>0</v>
       </c>
-      <c r="AE14" s="3" t="s">
-        <v>8</v>
+      <c r="AE14" s="3">
+        <v>0</v>
       </c>
       <c r="AF14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG14" s="3">
-        <v>0</v>
+      <c r="AG14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AH14" s="3">
         <v>0</v>
@@ -1580,70 +1599,73 @@
         <v>0</v>
       </c>
       <c r="AK14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL14" s="3">
         <v>1200</v>
       </c>
-      <c r="AL14" s="3">
-        <v>0</v>
-      </c>
       <c r="AM14" s="3">
         <v>0</v>
       </c>
       <c r="AN14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO14" s="3">
         <v>-200</v>
       </c>
-      <c r="AO14" s="3">
-        <v>0</v>
-      </c>
       <c r="AP14" s="3">
         <v>0</v>
       </c>
+      <c r="AQ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>82000</v>
+      </c>
+      <c r="E15" s="3">
         <v>75000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>83000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>81000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>79000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>70000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>76000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>70000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>68000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>70000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>73000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>71400</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>72600</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>68000</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1719,8 +1741,11 @@
       <c r="AP15" s="3">
         <v>0</v>
       </c>
+      <c r="AQ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1760,252 +1785,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>19302000</v>
+      </c>
+      <c r="E17" s="3">
         <v>18544000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>18987000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>19109000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>17944000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>17096000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>17230000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>16696000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>16198000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>14227000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>14311500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>14073500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>14846000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>13680000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>12374500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>12568800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>12086200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>11391300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>11229600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>11659400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>10843600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>9515300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>9247900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>8962600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>8642000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>8395400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>9348500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>8466800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>8153500</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>7678900</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>7740600</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>7317500</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>7090000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>6476500</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>6388200</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>6497200</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>6001100</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>5637600</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>5547500</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>5636400</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>4297000</v>
+      </c>
+      <c r="E18" s="3">
         <v>3636000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>3751000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>3393000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>4051000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>3306000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>3037000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>3016000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1929000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>3010000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>2573000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1479900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>501400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>617700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1088400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>205600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-572900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>444500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1255500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>193200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1055600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>1924300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>2162400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>1979900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>2325200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>922700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>1386300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>1057800</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>1291000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>1614900</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>288200</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>1172500</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>921800</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>947600</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>726900</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>288800</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>598000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>678300</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>574600</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>293800</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2048,8 +2080,9 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -2092,8 +2125,8 @@
       <c r="P20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
+      <c r="Q20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R20" s="3">
         <v>0</v>
@@ -2170,147 +2203,153 @@
       <c r="AP20" s="3">
         <v>0</v>
       </c>
+      <c r="AQ20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>4379000</v>
+      </c>
+      <c r="E21" s="3">
         <v>3711000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>3834000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>3474000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>4130000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>3376000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>3113000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>3086000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1997000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>3080000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>2646000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1551300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>574000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>685700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1172000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>288900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-488900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>530200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1345900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>282300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1136400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>2001400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>2250200</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>2065000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>2407000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>999800</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1469700</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1130000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1371000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1685400</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>358800</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1241700</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>985500</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>1006500</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>788100</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>348700</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>656500</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>734800</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>632900</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>345800</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>88000</v>
+      </c>
+      <c r="E22" s="3">
         <v>70000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>69000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>70000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>69000</v>
-      </c>
-      <c r="H22" s="3">
-        <v>70000</v>
       </c>
       <c r="I22" s="3">
         <v>70000</v>
@@ -2319,347 +2358,356 @@
         <v>70000</v>
       </c>
       <c r="K22" s="3">
+        <v>70000</v>
+      </c>
+      <c r="L22" s="3">
         <v>69000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>70000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>69300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>69700</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>65700</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>63300</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>63100</v>
       </c>
       <c r="R22" s="3">
         <v>63100</v>
       </c>
       <c r="S22" s="3">
+        <v>63100</v>
+      </c>
+      <c r="T22" s="3">
         <v>63000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>54300</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>51600</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>54200</v>
-      </c>
-      <c r="W22" s="3">
-        <v>56400</v>
       </c>
       <c r="X22" s="3">
         <v>56400</v>
       </c>
       <c r="Y22" s="3">
+        <v>56400</v>
+      </c>
+      <c r="Z22" s="3">
         <v>56200</v>
-      </c>
-      <c r="Z22" s="3">
-        <v>56400</v>
       </c>
       <c r="AA22" s="3">
         <v>56400</v>
       </c>
       <c r="AB22" s="3">
+        <v>56400</v>
+      </c>
+      <c r="AC22" s="3">
         <v>48000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>47400</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>47500</v>
-      </c>
-      <c r="AE22" s="3">
-        <v>47400</v>
       </c>
       <c r="AF22" s="3">
         <v>47400</v>
       </c>
       <c r="AG22" s="3">
+        <v>47400</v>
+      </c>
+      <c r="AH22" s="3">
         <v>46000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>42000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>41700</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>36800</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>35500</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>37400</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>43400</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>36800</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>37100</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>35300</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>4209000</v>
+      </c>
+      <c r="E23" s="3">
         <v>3566000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>3682000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>3323000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>3982000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>3236000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>2967000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>2946000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1860000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>2940000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>2503700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1410200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>435700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>554400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1025300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>142500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-635900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>390200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1203900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>139000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>999200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1867900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>2106200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1923500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>2268800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>874700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1338900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1010300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1243600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1567500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>242200</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>1130500</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>880100</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>910800</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>691400</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>251400</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>554600</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>641500</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>537500</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>258500</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>898000</v>
+      </c>
+      <c r="E24" s="3">
         <v>748000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>731000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>708000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>807000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>669000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>611000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>612000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>401000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>609000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>515300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>288900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>90300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>106500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>198900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>18400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-93000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>76300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>241600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>20500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>209100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>387900</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>421900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>392700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>478400</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>175600</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>264300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>166700</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>264600</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>484700</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-17600</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>200300</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>178900</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>181000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>210600</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>36600</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>181900</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>211200</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>139400</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>53000</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2780,252 +2828,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>3311000</v>
+      </c>
+      <c r="E26" s="3">
         <v>2818000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>2951000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>2615000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>3175000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>2567000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>2356000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>2334000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1459000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>2331000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1988400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1121300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>345400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>447900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>826400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>124100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-542900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>313900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>962300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>118500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>790100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1480000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1684300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>1530800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>1790400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>699100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>1074600</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>843600</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>979000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>1082800</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>259800</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>930200</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>701200</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>729800</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>480800</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>214800</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>372700</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>430300</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>398100</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>205500</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>3311000</v>
+      </c>
+      <c r="E27" s="3">
         <v>2818000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>2951000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>2615000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>3175000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>2567000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>2356000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>2334000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1459000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>2314000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1977600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1110900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>335900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>440600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>819600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>117400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-549600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>307200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>955500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>111800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>783400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>1473300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>1677500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>1524100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>1783700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>692400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>1064000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>835000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>972700</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>1071700</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>257900</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>921700</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>697500</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>716800</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>476800</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>224000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>367600</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>424300</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>383200</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>198700</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3146,8 +3203,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3232,8 +3292,8 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-      <c r="AE29" s="3" t="s">
-        <v>8</v>
+      <c r="AE29" s="3">
+        <v>0</v>
       </c>
       <c r="AF29" s="3" t="s">
         <v>8</v>
@@ -3250,12 +3310,12 @@
       <c r="AJ29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AK29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL29" s="3">
         <v>99500</v>
       </c>
-      <c r="AL29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AM29" s="3" t="s">
         <v>8</v>
       </c>
@@ -3268,8 +3328,11 @@
       <c r="AP29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3390,8 +3453,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3512,8 +3578,11 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3556,8 +3625,8 @@
       <c r="P32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
+      <c r="Q32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R32" s="3">
         <v>0</v>
@@ -3634,130 +3703,136 @@
       <c r="AP32" s="3">
         <v>0</v>
       </c>
+      <c r="AQ32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>3311000</v>
+      </c>
+      <c r="E33" s="3">
         <v>2818000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>2951000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>2615000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>3175000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>2567000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>2356000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>2334000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1459000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>2331000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1988400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1121300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>345400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>447900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>819600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>117400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-549600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>307200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>955500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>111800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>783400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>1473300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1677500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>1524100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>1783700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>692400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>1064000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>835000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>972700</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>1071700</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>257900</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>921700</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>697500</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>716800</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>576300</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>224000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>367600</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>424300</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>383200</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>198700</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3878,257 +3953,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>3311000</v>
+      </c>
+      <c r="E35" s="3">
         <v>2818000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>2951000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>2615000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>3175000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>2567000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>2356000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>2334000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1459000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>2331000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1988400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1121300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>345400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>447900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>819600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>117400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-549600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>307200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>955500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>111800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>783400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>1473300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1677500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>1524100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>1783700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>692400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>1064000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>835000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>972700</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>1071700</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>257900</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>921700</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>697500</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>716800</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>576300</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>224000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>367600</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>424300</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>383200</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>198700</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4171,8 +4255,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4215,175 +4300,179 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>178000</v>
+      </c>
+      <c r="E41" s="3">
         <v>162000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>125000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>173000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>125000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>195000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>143000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>136100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>90200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>154500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>85000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>123500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>163900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>273700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>203500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>350900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>226100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>272700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>187100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>270600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>99500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>122900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>76500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>90100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>108000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>369500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>226200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>45900</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>91900</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>158000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>69500</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>121900</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>154800</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>190100</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>265000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>224900</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>161000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>214500</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>211500</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>143400</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1978000</v>
+      </c>
+      <c r="E42" s="3">
         <v>2126000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>10005000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>1515000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>2103000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>2595000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>615000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>756500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>733400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>1326700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>1790000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>1795200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>1494300</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>2524100</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
-      </c>
       <c r="R42" s="3">
         <v>0</v>
       </c>
@@ -4459,130 +4548,136 @@
       <c r="AP42" s="3">
         <v>0</v>
       </c>
+      <c r="AQ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>17156000</v>
+      </c>
+      <c r="E43" s="3">
         <v>17614000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>15362000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>16519000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>16521000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>16811000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>14369000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>15140000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>14544500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>14192500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>11958000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>12408000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>12317300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>12411400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>10416900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>10867700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>10561800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>10519000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>9399500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>10246700</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>9436200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>9218800</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>8160100</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>8574300</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>7557400</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>7568300</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>7507300</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>7687200</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>7167100</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>7189800</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>6497100</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>6776600</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>6230200</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>6043800</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>5422500</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>5519900</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>5091300</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>4850700</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>4509200</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>4743600</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4625,8 +4720,8 @@
       <c r="P44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -4703,53 +4798,56 @@
       <c r="AP44" s="3">
         <v>0</v>
       </c>
+      <c r="AQ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>4647000</v>
+      </c>
+      <c r="E45" s="3">
         <v>4688000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>4753000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>4910000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>4950000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>5150000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>5359000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>5592200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>5597900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>5637400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>5609000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>5790900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>5930600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>5983500</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
-      </c>
       <c r="R45" s="3">
         <v>0</v>
       </c>
@@ -4825,53 +4923,56 @@
       <c r="AP45" s="3">
         <v>0</v>
       </c>
+      <c r="AQ45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>24176000</v>
+      </c>
+      <c r="E46" s="3">
         <v>24805000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>30455000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>23344000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>23972000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>25069000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>20846000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>21859700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>21268300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>21534300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>19707000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>20367500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>20164600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>21477200</v>
       </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
       <c r="R46" s="3">
         <v>0</v>
       </c>
@@ -4947,374 +5048,386 @@
       <c r="AP46" s="3">
         <v>0</v>
       </c>
+      <c r="AQ46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>95243000</v>
+      </c>
+      <c r="E47" s="3">
         <v>92005000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>87368000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>92994000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>86507000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>81069000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>79635000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>78643200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>71622100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>67711300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>64209000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>60075300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>57771300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>54162300</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>53548300</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>52330400</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>51929500</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>53186400</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>51514100</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>52287400</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>50942800</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>47400600</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>47530300</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>45764300</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>43777900</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>40342300</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>39254300</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>38573700</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>36814600</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>34512500</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>33567400</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>32350600</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>30921200</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>29251600</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>27274700</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>26994700</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>25978400</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>24303000</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>23482600</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>23521200</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>922000</v>
+      </c>
+      <c r="E48" s="3">
         <v>792000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>982000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>790000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>820000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>854000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>983000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>688800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>713500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>756300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1054000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>919800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>989000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>949000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1164500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1067100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1124700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1104400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1309900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1161000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1086400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1077400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1271500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1355700</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>1359800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>1391700</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>1213700</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>1214200</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>1174900</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>1127300</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>1131700</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>1139300</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>1116400</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>1112000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>1119600</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>1129400</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>1152100</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>1166000</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>1177100</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>1115000</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2211000</v>
+      </c>
+      <c r="E49" s="3">
         <v>2131000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2044000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2164000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2110000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2068000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1961000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2031600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1938300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1818200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1915000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>2034900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1991300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1935600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>314200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>319700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>325100</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>555400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>570000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>584600</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>599200</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>609900</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>624100</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>638200</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>652400</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>666500</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>681000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>695600</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>711400</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>729400</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>747300</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>765300</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>783300</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>801300</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>819300</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>837300</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>854500</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>866700</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>882200</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>897700</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5435,8 +5548,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5557,130 +5673,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1692000</v>
+      </c>
+      <c r="E52" s="3">
         <v>1734000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1404000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1581000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1438000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1489000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1324000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1381200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1349800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1276000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>742000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>898000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>830500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>826000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1148900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1283900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>970000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>385100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>15000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>14900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>15100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>300</v>
       </c>
-      <c r="Y52" s="3">
-        <v>0</v>
-      </c>
       <c r="Z52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA52" s="3">
         <v>1000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1100</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>35500</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1200</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>300</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>700</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>48700</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>800</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>2900</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>6500</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>10300</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>31400</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>800</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>500</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>14900</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>22300</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5801,130 +5923,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>124925000</v>
+      </c>
+      <c r="E54" s="3">
         <v>122209000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>123039000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>121535000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>115480000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>111409000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>105745000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>105202500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>97893000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>94127900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>88691000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>85652600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>82945200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>80407100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>75465000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>75524200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>73057200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>73929600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>71132300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>72618100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>69824300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>65413300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>64098300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>62906000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>59406100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>56265200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>54910500</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>54008100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>51324200</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>48850300</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>46575000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>45543700</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>43363500</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>41330900</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>38701200</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>38932600</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>36689800</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>34810500</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>33427500</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>33620800</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5967,8 +6095,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6011,130 +6140,134 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>54178000</v>
+      </c>
+      <c r="E57" s="3">
         <v>52690000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>52135000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>51825000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>49343000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>47814000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>46303000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>45910400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>43898400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>41541600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>40902000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>40194600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>39029300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>37079000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>5395600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>5931900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>5931200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>6688700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>5829700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>6394900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>6021800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>5770400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>4776800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>10568000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>5393700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>5157200</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>4617000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>5222900</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>4867500</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>4594300</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>5046500</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>3924100</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>3922300</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>3414300</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>2825900</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>3272700</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>3153200</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>2939400</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>2495500</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>2722200</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -6142,11 +6275,11 @@
         <v>1000000</v>
       </c>
       <c r="E58" s="3">
+        <v>1000000</v>
+      </c>
+      <c r="F58" s="3">
         <v>90000</v>
       </c>
-      <c r="F58" s="3">
-        <v>0</v>
-      </c>
       <c r="G58" s="3">
         <v>0</v>
       </c>
@@ -6196,26 +6329,26 @@
         <v>0</v>
       </c>
       <c r="W58" s="3">
-        <v>499900</v>
+        <v>0</v>
       </c>
       <c r="X58" s="3">
         <v>499900</v>
       </c>
       <c r="Y58" s="3">
+        <v>499900</v>
+      </c>
+      <c r="Z58" s="3">
         <v>499800</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>499700</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>499600</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>499500</v>
       </c>
-      <c r="AC58" s="3">
-        <v>0</v>
-      </c>
       <c r="AD58" s="3">
         <v>0</v>
       </c>
@@ -6255,175 +6388,181 @@
       <c r="AP58" s="3">
         <v>0</v>
       </c>
+      <c r="AQ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>27459000</v>
+      </c>
+      <c r="E59" s="3">
         <v>28651000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>33278000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>26846000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>26335000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>27450000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>26637000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>24772500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>23689400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>23869100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>20446000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>21007800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>20070100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>20047600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>17430800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>17796900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>17274800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>17049900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>15855200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>16729900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>15614400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>15104400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>16311000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>14444100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>13238000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>12830400</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>13764200</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>12526500</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>11796700</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>11603600</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>10686500</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>11009200</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>10245900</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>9837800</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>9558600</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>9005300</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>8407700</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>7945000</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>7863700</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>7792400</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>82637000</v>
+      </c>
+      <c r="E60" s="3">
         <v>82341000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>85503000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>78671000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>75678000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>75264000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>72940000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>70682900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>67587800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>65410700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>61348000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>61202400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>59099400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>57126600</v>
       </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
       <c r="R60" s="3">
         <v>0</v>
       </c>
@@ -6499,175 +6638,181 @@
       <c r="AP60" s="3">
         <v>0</v>
       </c>
+      <c r="AQ60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>7387000</v>
+      </c>
+      <c r="E61" s="3">
         <v>7386000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>7012000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>6896000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>6895000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>6894000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>7089000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>6891800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>6890700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>6889700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>7066000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>6887600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>6886500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>6389300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>6388300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>6387400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>6386500</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>6385600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>4898800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>4898200</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>4897600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>4896900</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>4896300</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>4895700</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>4895100</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>4894500</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>4407100</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>4406500</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>4406000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>4405400</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>4404900</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>3859900</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>3859500</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>3859200</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>3306300</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>3312200</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>3383400</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>3111700</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>3148200</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>3153900</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>568000</v>
+      </c>
+      <c r="E62" s="3">
         <v>443000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>200000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>523000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>303000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>297000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>125000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>468500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>74100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>16200</v>
       </c>
-      <c r="M62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N62" s="3">
+      <c r="N62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O62" s="3">
         <v>167300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>248000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>22800</v>
       </c>
-      <c r="Q62" s="3">
-        <v>0</v>
-      </c>
       <c r="R62" s="3">
         <v>0</v>
       </c>
@@ -6678,73 +6823,76 @@
         <v>0</v>
       </c>
       <c r="U62" s="3">
+        <v>0</v>
+      </c>
+      <c r="V62" s="3">
         <v>152900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>110700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>219400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>241500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>310000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>227900</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>197100</v>
       </c>
-      <c r="AB62" s="3">
-        <v>0</v>
-      </c>
       <c r="AC62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD62" s="3">
         <v>118000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>136000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>134500</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>38500</v>
       </c>
-      <c r="AG62" s="3">
-        <v>0</v>
-      </c>
       <c r="AH62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI62" s="3">
         <v>53500</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>46000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>53200</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>135000</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>201500</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>191800</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>168400</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>111300</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>156900</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6865,8 +7013,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6987,8 +7138,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7109,130 +7263,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>90592000</v>
+      </c>
+      <c r="E66" s="3">
         <v>90170000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>92716000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>86090000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>82876000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>82455000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>80154000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>78043200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>74552600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>72316600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>68414000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>68257300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>66233900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>63538700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>59574000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>60748000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>57404500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>56878400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>52900700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>54060000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>51148700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>47576800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>47059700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>44818800</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>42735500</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>41913700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>41237300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>39884800</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>37993400</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>36739600</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>35753200</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>33684900</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>32362700</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>31007700</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>29416400</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>29643200</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>27698300</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>26287600</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>25470400</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>25526100</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7275,8 +7435,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7397,8 +7558,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7519,8 +7683,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7552,10 +7719,10 @@
         <v>0</v>
       </c>
       <c r="M70" s="3">
+        <v>0</v>
+      </c>
+      <c r="N70" s="3">
         <v>494000</v>
-      </c>
-      <c r="N70" s="3">
-        <v>493900</v>
       </c>
       <c r="O70" s="3">
         <v>493900</v>
@@ -7624,7 +7791,7 @@
         <v>493900</v>
       </c>
       <c r="AK70" s="3">
-        <v>0</v>
+        <v>493900</v>
       </c>
       <c r="AL70" s="3">
         <v>0</v>
@@ -7641,8 +7808,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7763,130 +7933,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>32261000</v>
+      </c>
+      <c r="E72" s="3">
         <v>29612000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>27327000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>32437000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>29921000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>26732000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>24283000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>24631700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>22410000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>21020500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>18801000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>17380900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>16350400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>16080100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>15721200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>14987500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>14967700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>15569600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>15339700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>15390000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>15401000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>14679600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>13354900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>14427700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>13001800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>11266200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>10679600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>10995200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>10276400</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>9358100</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>8386600</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>9602100</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>8720400</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>8017900</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>6031700</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>6116500</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>5908800</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>5543400</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>5140400</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>5183100</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8007,8 +8183,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8129,8 +8308,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8251,130 +8433,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>34333000</v>
+      </c>
+      <c r="E76" s="3">
         <v>32039000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>30323000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>35445000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>32604000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>28954000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>25591000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>27159300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>23340400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>21811300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>19783000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>16901400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>16217400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>16374500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>15397100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>14282300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>15158800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>16557300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>17737700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>18064200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>18181700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>17342600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>16544700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>17593300</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>16176700</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>13857600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>13179300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>13629400</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>12836900</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>11616800</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>10327900</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>11364900</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>10506900</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>9829300</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>9284800</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>9289400</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>8991500</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>8522900</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>7957100</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>8094700</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8495,257 +8683,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>3311000</v>
+      </c>
+      <c r="E81" s="3">
         <v>2818000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>2951000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>2615000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>3175000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>2567000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>2356000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>2334000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1459000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>2331000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1988400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1121300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>345400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>447900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>819600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>117400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-549600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>307200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>955500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>111800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>783400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>1473300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1677500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>1524100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>1783700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>692400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>1064000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>835000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>972700</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>1071700</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>257900</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>921700</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>697500</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>716800</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>576300</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>224000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>367600</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>424300</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>383200</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>198700</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8788,130 +8985,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>79000</v>
+      </c>
+      <c r="E83" s="3">
         <v>70000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>76000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>70000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>68000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>70000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>73000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>71400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>72600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>68000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>78100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>77900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>78500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>71100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>83600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>83300</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>84000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>85700</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>90400</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>89100</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>80800</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>77100</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>87800</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>85100</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>81800</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>77100</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>83400</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>72200</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>80000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>70500</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>70600</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>69200</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>63700</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>58900</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>61200</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>59900</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>58500</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>56500</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>58300</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>52000</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9032,8 +9233,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9154,8 +9358,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9276,8 +9483,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9398,8 +9608,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9520,130 +9733,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>3607000</v>
+      </c>
+      <c r="E89" s="3">
         <v>4367000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>3170000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>5195000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>4040000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>5143000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>3008000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>4609000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>3267000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>4235000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2437000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>3419500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>2337000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>2449500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>929600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>2027300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1389600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>2502300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>452100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>2371200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>2323900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>2614500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1547300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1479700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>2252800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1625800</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1128200</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1758700</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1506200</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1868500</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1083300</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>1718200</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>1736200</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>1747100</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>533700</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>1186400</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>917900</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>1118800</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>473100</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>688300</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9686,130 +9905,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-138000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-63000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-121000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-66000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-102000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-59000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-110000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-57000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-68000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-50000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-82100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-36300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-90400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-43200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-47000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-108300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-63700</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-73000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-55200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-89800</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-48000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-50500</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-47100</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-65700</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-48300</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-62400</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-82300</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-78000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-127400</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-75800</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-101200</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-62800</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-66200</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-35800</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-46000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-36500</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-38200</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-70000</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-267900</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>56100</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9930,8 +10153,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10052,130 +10278,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2921000</v>
+      </c>
+      <c r="E94" s="3">
         <v>2637000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-3099000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-5047000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-4040000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-2341000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-2942000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-4420000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-3263000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-3124000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-2345700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-3352100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-2867000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-2277200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-995100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1781500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1377100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-3802500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>455300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1556600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-2243400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>224900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-1466200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-1380400</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-2217300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-1053800</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-885300</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-1673900</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-1501700</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-277400</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-1675200</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-1700400</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-1775600</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-2180600</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-507400</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-996900</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-1239800</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-662600</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-340200</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-1135200</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10218,40 +10450,41 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>58000</v>
+      </c>
+      <c r="E96" s="3">
         <v>7972000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>59000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>58000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>59000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>2695000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>59000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>58000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>59000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>498000</v>
-      </c>
-      <c r="M96" s="3">
-        <v>58500</v>
       </c>
       <c r="N96" s="3">
         <v>58500</v>
@@ -10263,7 +10496,7 @@
         <v>58500</v>
       </c>
       <c r="Q96" s="3">
-        <v>-58500</v>
+        <v>58500</v>
       </c>
       <c r="R96" s="3">
         <v>-58500</v>
@@ -10275,44 +10508,44 @@
         <v>-58500</v>
       </c>
       <c r="U96" s="3">
+        <v>-58500</v>
+      </c>
+      <c r="V96" s="3">
         <v>-935000</v>
-      </c>
-      <c r="V96" s="3">
-        <v>-58500</v>
       </c>
       <c r="W96" s="3">
         <v>-58500</v>
       </c>
       <c r="X96" s="3">
+        <v>-58500</v>
+      </c>
+      <c r="Y96" s="3">
         <v>-2694500</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-58600</v>
-      </c>
-      <c r="Z96" s="3">
-        <v>-58500</v>
       </c>
       <c r="AA96" s="3">
         <v>-58500</v>
       </c>
       <c r="AB96" s="3">
+        <v>-58500</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-1375400</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-58500</v>
-      </c>
-      <c r="AD96" s="3">
-        <v>-58400</v>
       </c>
       <c r="AE96" s="3">
         <v>-58400</v>
       </c>
       <c r="AF96" s="3">
+        <v>-58400</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-1467900</v>
       </c>
-      <c r="AG96" s="3">
-        <v>0</v>
-      </c>
       <c r="AH96" s="3">
         <v>0</v>
       </c>
@@ -10320,11 +10553,11 @@
         <v>0</v>
       </c>
       <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK96" s="3">
         <v>-654900</v>
       </c>
-      <c r="AK96" s="3">
-        <v>0</v>
-      </c>
       <c r="AL96" s="3">
         <v>0</v>
       </c>
@@ -10332,16 +10565,19 @@
         <v>0</v>
       </c>
       <c r="AN96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO96" s="3">
         <v>-395400</v>
       </c>
-      <c r="AO96" s="3">
-        <v>0</v>
-      </c>
       <c r="AP96" s="3">
         <v>0</v>
       </c>
+      <c r="AQ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10462,8 +10698,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10584,8 +10823,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10706,130 +10948,136 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-672000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-6963000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-118000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-98000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-72000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-2749000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-59000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-144000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-70000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1043000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-129800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-108500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>420900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-104600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-78900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-121000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-59300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>1385400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-990800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-643700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-89100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-2792700</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-95700</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-117300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-296800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-429000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-72900</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-131500</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-59100</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-1507400</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>544200</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-52800</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>500</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>354800</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-6600</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-109500</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>268400</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-453200</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-34000</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>439200</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10872,8 +11120,8 @@
       <c r="P101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -10926,21 +11174,21 @@
       <c r="AH101" s="3">
         <v>0</v>
       </c>
-      <c r="AI101" s="3" t="s">
-        <v>8</v>
+      <c r="AI101" s="3">
+        <v>0</v>
       </c>
       <c r="AJ101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AK101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL101" s="3">
         <v>-700</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>400</v>
       </c>
-      <c r="AM101" s="3">
-        <v>0</v>
-      </c>
       <c r="AN101" s="3">
         <v>0</v>
       </c>
@@ -10948,128 +11196,134 @@
         <v>0</v>
       </c>
       <c r="AP101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ101" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>14000</v>
+      </c>
+      <c r="E102" s="3">
         <v>41000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-47000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>50000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-72000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>53000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>7000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>45000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-66000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>68000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-38500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-41100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-109100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>67700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-144400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>124800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-46800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>85200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-83400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>170900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-8600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>46700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-14600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-18000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-261300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>143000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>181200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-46700</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-65800</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>83700</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-47700</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-35000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-38900</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-78700</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>19000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>80400</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-53500</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>3000</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>82700</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>8700</v>
       </c>
     </row>
